--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_43.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4710028.863049883</v>
+        <v>4670074.765810343</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6766202.409523279</v>
+        <v>6772506.086290956</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6766202.409523279</v>
+        <v>6772506.086290956</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3024735.260324415</v>
+        <v>3031871.820627598</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3024735.260324415</v>
+        <v>3031871.820627598</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44430153.78042449</v>
+        <v>44435301.95724843</v>
       </c>
     </row>
   </sheetData>
@@ -657,13 +657,13 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -675,16 +675,16 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>98.12488247690044</v>
+        <v>815</v>
       </c>
       <c r="L2" t="n">
-        <v>617.5923040188184</v>
+        <v>279.7604168367411</v>
       </c>
       <c r="M2" t="n">
         <v>298.9910820919849</v>
@@ -705,16 +705,16 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>191.3386006767583</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>476.4226167239435</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>285.2549665268088</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -787,10 +787,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>57.72562438342276</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -906,49 +906,49 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>100.2478051614514</v>
       </c>
       <c r="H5" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>767.4274152265739</v>
+        <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>279.7604168366991</v>
       </c>
       <c r="M5" t="n">
-        <v>815</v>
+        <v>298.9910820919849</v>
       </c>
       <c r="N5" t="n">
         <v>195.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>619.2514644189524</v>
+        <v>371.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>442.2171995050529</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
         <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>387.8730357844535</v>
       </c>
       <c r="S6" t="n">
-        <v>176.3519374503314</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1143,7 +1143,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>351.1264039897461</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>408.0096587035274</v>
@@ -1152,40 +1152,40 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>419.7382696589336</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>66.13418277956056</v>
+        <v>98.12488247690055</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>298.9910820919849</v>
+      </c>
+      <c r="N8" t="n">
+        <v>195.5855355810472</v>
+      </c>
+      <c r="O8" t="n">
         <v>815</v>
       </c>
-      <c r="M8" t="n">
-        <v>815</v>
-      </c>
-      <c r="N8" t="n">
-        <v>281.3919627881424</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>617.5923040187447</v>
       </c>
       <c r="Q8" t="n">
-        <v>798.7814999999999</v>
+        <v>371.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>249.2212965486107</v>
+        <v>345.7117294230463</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1194,10 +1194,10 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>73.16906773709609</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>147.2737972923793</v>
+        <v>272.8313344893809</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>127.9306976023938</v>
+        <v>153.8092964306882</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
@@ -1535,7 +1535,7 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9.467758489792265</v>
       </c>
       <c r="G13" t="n">
         <v>20.04387284153003</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>30.85598296821916</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1656,13 +1656,13 @@
         <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>335.6755817285639</v>
+        <v>207.443205796785</v>
       </c>
       <c r="U14" t="n">
-        <v>388.5225121008489</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>387.3734759809475</v>
@@ -1671,7 +1671,7 @@
         <v>341.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>260.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>417.2070674528527</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>111.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S17" t="n">
         <v>215.8481678023229</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
-        <v>339.4016293563778</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>219.2983591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>255.2652880979692</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>339.4016293563778</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S23" t="n">
         <v>215.8481678023229</v>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>255.2652880979692</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2559,13 +2559,13 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>20.80957970762735</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4.62282255364775</v>
       </c>
       <c r="H26" t="n">
         <v>183.0096587035274</v>
@@ -2604,16 +2604,16 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>367.2818334606677</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>340.7767994885277</v>
+        <v>118.845874018486</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>236.9993129555745</v>
+        <v>232.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>200.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>161.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>159.3632896068686</v>
+        <v>35.8363418625441</v>
       </c>
       <c r="F29" t="n">
-        <v>159.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>50.1587575305075</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,28 +2835,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.878598828294457</v>
+        <v>1.878598828294457</v>
       </c>
       <c r="S29" t="n">
-        <v>249.8481678023229</v>
+        <v>245.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>341.6755817285639</v>
+        <v>337.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>404.2212965486107</v>
+        <v>400.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>384.8510241668239</v>
+        <v>380.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>393.3734759809475</v>
+        <v>389.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>347.2818334606677</v>
+        <v>343.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>266.3174326828064</v>
+        <v>262.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>139.5565566463266</v>
+        <v>135.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>116.0999124455193</v>
+        <v>112.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>102.9376868977026</v>
+        <v>98.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>97.67209722191262</v>
+        <v>93.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>94.63624233787687</v>
+        <v>90.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>80.73953587502734</v>
+        <v>76.73953587502734</v>
       </c>
       <c r="H30" t="n">
-        <v>87.16808718642113</v>
+        <v>83.16808718642113</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>302.2737972923793</v>
+        <v>298.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>221.5639999646113</v>
+        <v>217.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>160.3577652175138</v>
+        <v>156.3577652175138</v>
       </c>
       <c r="U30" t="n">
-        <v>155.2103597601867</v>
+        <v>151.2103597601867</v>
       </c>
       <c r="V30" t="n">
-        <v>169.5106671915202</v>
+        <v>165.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>187.3731429098285</v>
+        <v>183.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>174.8627394453875</v>
+        <v>170.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.3913927661343</v>
+        <v>150.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2948,16 +2948,16 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>27.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>40.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>35.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>29.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2972,13 +2972,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>43.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>22.87190767164101</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>275.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>476.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>34.09948073011024</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.443645430107551</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3048,28 +3048,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589336</v>
+        <v>375.7382696589465</v>
       </c>
       <c r="K32" t="n">
-        <v>405.8322678378306</v>
+        <v>771</v>
       </c>
       <c r="L32" t="n">
-        <v>304.7028254483104</v>
+        <v>771</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820919849</v>
+        <v>657.1104099705364</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810472</v>
+        <v>151.5855355810602</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579117</v>
+        <v>265.4165272191283</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>359.2212965486107</v>
       </c>
       <c r="V32" t="n">
-        <v>334.3076155522384</v>
+        <v>339.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>348.3734759809475</v>
+        <v>335.068467366362</v>
       </c>
       <c r="X32" t="n">
         <v>302.2818334606677</v>
@@ -3218,19 +3218,19 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>176.9168637871031</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>350.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>397.4478973282775</v>
+        <v>52.36893078764645</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>435.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>436.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>186.4559043409888</v>
+        <v>191.9993129555745</v>
       </c>
       <c r="C35" t="n">
         <v>159.4745782429939</v>
@@ -3273,7 +3273,7 @@
         <v>114.3632896068686</v>
       </c>
       <c r="F35" t="n">
-        <v>114.8896287080119</v>
+        <v>101.5846200934261</v>
       </c>
       <c r="G35" t="n">
         <v>113.7573722870162</v>
@@ -3285,28 +3285,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.7382696589336</v>
+        <v>723.445655019903</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>360.540647884545</v>
+        <v>762.8578586788261</v>
       </c>
       <c r="M35" t="n">
-        <v>773</v>
+        <v>254.9910820920049</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810472</v>
+        <v>151.5855355810675</v>
       </c>
       <c r="O35" t="n">
-        <v>606.9855274935954</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.9706110579117</v>
+        <v>327.9706110579319</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3449,22 +3449,22 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>15.5457411918833</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>230.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>281.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>91.52316144052014</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>397.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>435.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>114.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>108.2139636724305</v>
+        <v>113.7573722870162</v>
       </c>
       <c r="H38" t="n">
         <v>118.0096587035274</v>
@@ -3522,28 +3522,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589336</v>
+        <v>375.7382696589611</v>
       </c>
       <c r="K38" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>762.5707986380528</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820919849</v>
+        <v>254.9910820920122</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355810472</v>
+        <v>151.5855355810747</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="P38" t="n">
-        <v>710.5350932861253</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.9706110579117</v>
+        <v>675.9650564595786</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>302.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>221.3174326828064</v>
+        <v>208.0124240682208</v>
       </c>
     </row>
     <row r="39">
@@ -3698,13 +3698,13 @@
         <v>350.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>397.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>435.839266425598</v>
+        <v>176.9168637871031</v>
       </c>
       <c r="R40" t="n">
-        <v>138.5254946897826</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>161.8428013747292</v>
+        <v>271.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>240.4745782429939</v>
+        <v>239.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>201.3391557398498</v>
+        <v>200.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>195.3632896068686</v>
+        <v>194.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>195.8896287080119</v>
+        <v>194.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>194.7573722870162</v>
+        <v>193.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>199.0096587035274</v>
+        <v>198.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,28 +3783,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>40.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>284.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>377.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>420.8510241668239</v>
+        <v>419.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>429.3734759809475</v>
+        <v>428.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>383.2818334606677</v>
+        <v>23.99510429496184</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>301.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3814,28 +3814,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>175.5565566463266</v>
+        <v>174.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>152.0999124455193</v>
+        <v>151.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>138.9376868977026</v>
+        <v>137.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>133.6720972219126</v>
+        <v>132.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>130.6362423378769</v>
+        <v>129.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>116.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>123.1680871864211</v>
+        <v>122.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>8.126385891348534</v>
+        <v>7.126385891348534</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>311.7395716824499</v>
+        <v>337.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>257.5639999646113</v>
+        <v>256.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>196.3577652175138</v>
+        <v>195.3577652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>191.2103597601867</v>
+        <v>190.2103597601867</v>
       </c>
       <c r="V42" t="n">
-        <v>205.5106671915202</v>
+        <v>204.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>116.3239206424562</v>
       </c>
       <c r="X42" t="n">
-        <v>210.8627394453875</v>
+        <v>209.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>190.3913927661343</v>
+        <v>189.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>19.77112610161862</v>
+        <v>18.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.024566506257713</v>
+        <v>0.02456650625769896</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>17.37280983870968</v>
+        <v>16.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>318.9993129555745</v>
+        <v>321.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>286.4745782429939</v>
+        <v>289.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>247.3391557398498</v>
+        <v>250.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>40.9681617041538</v>
+        <v>244.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>241.8896287080119</v>
+        <v>244.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>240.7573722870162</v>
+        <v>243.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>245.0096587035274</v>
+        <v>248.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>87.87859882829446</v>
+        <v>90.87859882829446</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4029,19 +4029,19 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>489.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>466.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>475.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>217.846475696446</v>
       </c>
       <c r="Y44" t="n">
-        <v>348.3174326828064</v>
+        <v>351.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>221.5565566463266</v>
+        <v>224.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>198.0999124455193</v>
+        <v>201.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>184.9376868977026</v>
+        <v>187.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>179.6720972219126</v>
+        <v>182.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>176.6362423378769</v>
+        <v>179.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>162.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>169.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>54.12638589134853</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10.07926509047959</v>
+        <v>13.07926509047959</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4105,22 +4105,22 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>242.3577652175138</v>
+        <v>245.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>237.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>251.5106671915202</v>
+        <v>254.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>109.2465695938636</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>259.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>34.24888309240159</v>
+        <v>239.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510.568528253487</v>
+        <v>146.8501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>1056.553802755514</v>
+        <v>96.87586368209487</v>
       </c>
       <c r="D2" t="n">
-        <v>642.0698070586957</v>
+        <v>86.43227202568094</v>
       </c>
       <c r="E2" t="n">
-        <v>233.6220397790304</v>
+        <v>82.02490878641969</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6830208820487</v>
+        <v>77.08588988943801</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8876953396081</v>
+        <v>73.29056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7971309926107</v>
+        <v>65.2</v>
       </c>
       <c r="I2" t="n">
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>772.9339570940399</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L2" t="n">
         <v>924.2825542736812</v>
@@ -4348,25 +4348,25 @@
         <v>3006.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2813.315960095906</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2624.75476643069</v>
+        <v>1914.139042061433</v>
       </c>
       <c r="U2" t="n">
-        <v>2373.016083048255</v>
+        <v>1258.359954638594</v>
       </c>
       <c r="V2" t="n">
-        <v>2140.843331364595</v>
+        <v>777.1249882507718</v>
       </c>
       <c r="W2" t="n">
-        <v>1900.062042494951</v>
+        <v>536.3436993811277</v>
       </c>
       <c r="X2" t="n">
-        <v>1705.837968292256</v>
+        <v>342.1196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>1593.396117097502</v>
+        <v>229.6777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.2</v>
+        <v>2392.703909456524</v>
       </c>
       <c r="C3" t="n">
-        <v>65.2</v>
+        <v>2392.703909456524</v>
       </c>
       <c r="D3" t="n">
-        <v>65.2</v>
+        <v>2392.703909456524</v>
       </c>
       <c r="E3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="F3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="G3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="H3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="I3" t="n">
-        <v>65.2</v>
+        <v>2104.567579631464</v>
       </c>
       <c r="J3" t="n">
-        <v>189.156520175299</v>
+        <v>2228.524099806763</v>
       </c>
       <c r="K3" t="n">
-        <v>378.3493362696823</v>
+        <v>2417.716915901147</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6997978648824</v>
+        <v>2689.067377496347</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7803396077417</v>
+        <v>2775.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>869.06062421531</v>
+        <v>2908.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.103075899029</v>
+        <v>3147.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.632420368536</v>
+        <v>3260</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.632420368536</v>
+        <v>3085.172459504566</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.871008962092</v>
+        <v>2936.411048098123</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.634645361474</v>
+        <v>2869.174684497505</v>
       </c>
       <c r="T3" t="n">
-        <v>595.1823572629755</v>
+        <v>2863.76280043941</v>
       </c>
       <c r="U3" t="n">
-        <v>190.9294686163222</v>
+        <v>2863.550315833161</v>
       </c>
       <c r="V3" t="n">
-        <v>176.2722290289281</v>
+        <v>2848.893076245767</v>
       </c>
       <c r="W3" t="n">
-        <v>143.572084675566</v>
+        <v>2816.192931892404</v>
       </c>
       <c r="X3" t="n">
-        <v>123.5087114984068</v>
+        <v>2796.129558715245</v>
       </c>
       <c r="Y3" t="n">
-        <v>65.2</v>
+        <v>2392.703909456524</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1244.509930203872</v>
+        <v>1093.911188247601</v>
       </c>
       <c r="C4" t="n">
-        <v>1244.509930203872</v>
+        <v>1219.913194066037</v>
       </c>
       <c r="D4" t="n">
-        <v>1244.509930203872</v>
+        <v>1333.232338191037</v>
       </c>
       <c r="E4" t="n">
-        <v>1244.509930203872</v>
+        <v>1333.232338191037</v>
       </c>
       <c r="F4" t="n">
-        <v>1244.509930203872</v>
+        <v>1333.232338191037</v>
       </c>
       <c r="G4" t="n">
-        <v>1244.509930203872</v>
+        <v>1333.232338191037</v>
       </c>
       <c r="H4" t="n">
-        <v>1244.509930203872</v>
+        <v>1354.874364140741</v>
       </c>
       <c r="I4" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="J4" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="K4" t="n">
         <v>1576.007243076824</v>
@@ -4509,22 +4509,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>537.0771268912647</v>
+        <v>349.0014477324597</v>
       </c>
       <c r="V4" t="n">
-        <v>735.8985197772106</v>
+        <v>547.8228406184057</v>
       </c>
       <c r="W4" t="n">
-        <v>907.789438036888</v>
+        <v>719.7137588780831</v>
       </c>
       <c r="X4" t="n">
-        <v>1058.820229061082</v>
+        <v>870.7445499022766</v>
       </c>
       <c r="Y4" t="n">
-        <v>1170.229529740114</v>
+        <v>982.1538505813089</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1106.528124213083</v>
+        <v>395.9123998438258</v>
       </c>
       <c r="C5" t="n">
-        <v>1056.553802755514</v>
+        <v>345.9380783862562</v>
       </c>
       <c r="D5" t="n">
-        <v>1046.1102110991</v>
+        <v>335.4944867298423</v>
       </c>
       <c r="E5" t="n">
-        <v>1041.702847859838</v>
+        <v>331.0871234905811</v>
       </c>
       <c r="F5" t="n">
-        <v>1036.763828962857</v>
+        <v>326.1481045935994</v>
       </c>
       <c r="G5" t="n">
-        <v>628.9280993800121</v>
+        <v>224.8876953396081</v>
       </c>
       <c r="H5" t="n">
         <v>216.7971309926107</v>
@@ -4558,52 +4558,52 @@
         <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>65.2</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L5" t="n">
-        <v>872.05</v>
+        <v>924.2825542736812</v>
       </c>
       <c r="M5" t="n">
-        <v>855.6676767676768</v>
+        <v>1429.121360241373</v>
       </c>
       <c r="N5" t="n">
-        <v>1464.956529716114</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O5" t="n">
-        <v>2271.806529716114</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P5" t="n">
-        <v>3078.656529716114</v>
+        <v>2828.877889957487</v>
       </c>
       <c r="Q5" t="n">
         <v>3260</v>
       </c>
       <c r="R5" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2813.315960095906</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2220.714362390286</v>
+        <v>1914.139042061433</v>
       </c>
       <c r="U5" t="n">
-        <v>1968.975679007851</v>
+        <v>1258.359954638594</v>
       </c>
       <c r="V5" t="n">
-        <v>1736.80292732419</v>
+        <v>1026.187202954933</v>
       </c>
       <c r="W5" t="n">
-        <v>1496.021638454547</v>
+        <v>785.4059140852892</v>
       </c>
       <c r="X5" t="n">
-        <v>1301.797564251852</v>
+        <v>591.1818398825944</v>
       </c>
       <c r="Y5" t="n">
-        <v>1189.355713057098</v>
+        <v>478.7399886878405</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>416.6522089875784</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="C6" t="n">
-        <v>416.6522089875784</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="D6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="E6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>65.2</v>
@@ -4661,28 +4661,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>667.8306049216877</v>
+        <v>828.8414751317139</v>
       </c>
       <c r="S6" t="n">
-        <v>489.6973347698378</v>
+        <v>761.6051115310964</v>
       </c>
       <c r="T6" t="n">
-        <v>484.285450711743</v>
+        <v>756.1932274730017</v>
       </c>
       <c r="U6" t="n">
-        <v>484.0729661054938</v>
+        <v>755.9807428667524</v>
       </c>
       <c r="V6" t="n">
-        <v>469.4157265180997</v>
+        <v>741.3235032793583</v>
       </c>
       <c r="W6" t="n">
-        <v>436.7155821647376</v>
+        <v>708.6233589259962</v>
       </c>
       <c r="X6" t="n">
-        <v>416.6522089875784</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="Y6" t="n">
-        <v>416.6522089875784</v>
+        <v>284.5195817084329</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>440.0757524108052</v>
+        <v>476.647684463691</v>
       </c>
       <c r="C7" t="n">
-        <v>566.077758229241</v>
+        <v>602.6496902821268</v>
       </c>
       <c r="D7" t="n">
-        <v>679.3969023542411</v>
+        <v>715.9688344071269</v>
       </c>
       <c r="E7" t="n">
-        <v>797.2258065656541</v>
+        <v>833.7977386185399</v>
       </c>
       <c r="F7" t="n">
-        <v>921.5867791575896</v>
+        <v>958.1587112104754</v>
       </c>
       <c r="G7" t="n">
         <v>1074.993345044475</v>
@@ -4746,22 +4746,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="U7" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="V7" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="W7" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="X7" t="n">
-        <v>290.525934252978</v>
+        <v>253.4810461183666</v>
       </c>
       <c r="Y7" t="n">
-        <v>328.3184147445131</v>
+        <v>364.8903467973989</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1457.405934013821</v>
+        <v>702.4877201726792</v>
       </c>
       <c r="C8" t="n">
-        <v>1003.391208515847</v>
+        <v>652.5133987151096</v>
       </c>
       <c r="D8" t="n">
-        <v>992.947616859433</v>
+        <v>642.0698070586957</v>
       </c>
       <c r="E8" t="n">
-        <v>988.5402536201717</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F8" t="n">
-        <v>983.60123472319</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G8" t="n">
         <v>628.9280993800121</v>
@@ -4795,52 +4795,52 @@
         <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>448.0719498394611</v>
+        <v>65.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1156.448952311255</v>
+        <v>772.9339570940398</v>
       </c>
       <c r="L8" t="n">
-        <v>1140.066629078932</v>
+        <v>1548.113164393626</v>
       </c>
       <c r="M8" t="n">
-        <v>1123.684305846609</v>
+        <v>2052.951970361318</v>
       </c>
       <c r="N8" t="n">
-        <v>1646.3</v>
+        <v>2662.240823309755</v>
       </c>
       <c r="O8" t="n">
-        <v>2453.15</v>
+        <v>2645.858500077431</v>
       </c>
       <c r="P8" t="n">
-        <v>3260</v>
+        <v>2828.877889957487</v>
       </c>
       <c r="Q8" t="n">
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>3164.193769896644</v>
+        <v>2910.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2975.632576231427</v>
+        <v>2318.179446101837</v>
       </c>
       <c r="U8" t="n">
-        <v>2723.893892848992</v>
+        <v>1968.975679007851</v>
       </c>
       <c r="V8" t="n">
-        <v>2491.721141165332</v>
+        <v>1736.80292732419</v>
       </c>
       <c r="W8" t="n">
-        <v>2250.939852295688</v>
+        <v>1496.021638454547</v>
       </c>
       <c r="X8" t="n">
-        <v>1652.675374052589</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y8" t="n">
-        <v>1540.233522857835</v>
+        <v>785.3153090166938</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139.10814922939</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="C9" t="n">
-        <v>139.10814922939</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="D9" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="E9" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="F9" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="G9" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="H9" t="n">
         <v>65.2</v>
@@ -4898,28 +4898,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.871008962092</v>
+        <v>945.0452138136053</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.634645361474</v>
+        <v>877.8088502129879</v>
       </c>
       <c r="T9" t="n">
-        <v>595.1823572629755</v>
+        <v>872.3969661548931</v>
       </c>
       <c r="U9" t="n">
-        <v>594.9698726567262</v>
+        <v>872.1844815486438</v>
       </c>
       <c r="V9" t="n">
-        <v>580.3126330693322</v>
+        <v>857.5272419612497</v>
       </c>
       <c r="W9" t="n">
-        <v>547.61248871597</v>
+        <v>824.8270976078876</v>
       </c>
       <c r="X9" t="n">
-        <v>527.5491155388108</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.5491155388108</v>
+        <v>400.7233203903244</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>550.4401863476735</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="C10" t="n">
-        <v>676.4421921661093</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="D10" t="n">
-        <v>789.7613362911094</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="E10" t="n">
-        <v>907.5902405025224</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="F10" t="n">
-        <v>1031.951213094458</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G10" t="n">
-        <v>1185.357778981343</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H10" t="n">
-        <v>1354.874364140741</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I10" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J10" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="K10" t="n">
         <v>1576.007243076824</v>
@@ -4980,25 +4980,25 @@
         <v>65.2</v>
       </c>
       <c r="S10" t="n">
-        <v>65.2</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>176.2427569781556</v>
+        <v>537.0771268912647</v>
       </c>
       <c r="V10" t="n">
-        <v>176.2427569781556</v>
+        <v>735.8985197772106</v>
       </c>
       <c r="W10" t="n">
-        <v>176.2427569781556</v>
+        <v>907.789438036888</v>
       </c>
       <c r="X10" t="n">
-        <v>327.2735480023491</v>
+        <v>907.789438036888</v>
       </c>
       <c r="Y10" t="n">
-        <v>438.6828486813814</v>
+        <v>907.789438036888</v>
       </c>
     </row>
     <row r="11">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>421.1649250963513</v>
+        <v>447.3049239128102</v>
       </c>
       <c r="C11" t="n">
-        <v>194.4229268711049</v>
+        <v>220.5629256875638</v>
       </c>
       <c r="D11" t="n">
         <v>65.2</v>
@@ -5032,19 +5032,19 @@
         <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>774.9063663478685</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1581.756366347868</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>2092.605195076803</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2705.825514851566</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O11" t="n">
         <v>2821.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3260</v>
       </c>
       <c r="R11" t="n">
-        <v>3233.860001183541</v>
+        <v>3260</v>
       </c>
       <c r="S11" t="n">
-        <v>2961.286094312508</v>
+        <v>2987.426093128967</v>
       </c>
       <c r="T11" t="n">
-        <v>2595.957223879615</v>
+        <v>2622.097222696074</v>
       </c>
       <c r="U11" t="n">
-        <v>2167.450863729503</v>
+        <v>2193.590862545962</v>
       </c>
       <c r="V11" t="n">
-        <v>1758.510435278166</v>
+        <v>1784.650434094625</v>
       </c>
       <c r="W11" t="n">
-        <v>1340.961469640845</v>
+        <v>1367.101468457304</v>
       </c>
       <c r="X11" t="n">
-        <v>969.9697186704734</v>
+        <v>996.1097174869324</v>
       </c>
       <c r="Y11" t="n">
-        <v>680.7601907080427</v>
+        <v>706.9001895245017</v>
       </c>
     </row>
     <row r="12">
@@ -5108,19 +5108,19 @@
         <v>65.2</v>
       </c>
       <c r="I12" t="n">
-        <v>72.99487796756496</v>
+        <v>65.2</v>
       </c>
       <c r="J12" t="n">
-        <v>419.7013981428639</v>
+        <v>411.906520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>831.6442142372473</v>
+        <v>627.8199167834982</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.744675832447</v>
+        <v>1121.920378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.575217575307</v>
+        <v>1430.750920121558</v>
       </c>
       <c r="N12" t="n">
         <v>1786.781204729126</v>
@@ -5166,16 +5166,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>255.1569378623287</v>
+        <v>264.7203302762603</v>
       </c>
       <c r="C13" t="n">
-        <v>206.9496180158189</v>
+        <v>216.5130104297505</v>
       </c>
       <c r="D13" t="n">
-        <v>145.8019230102073</v>
+        <v>155.3653154241389</v>
       </c>
       <c r="E13" t="n">
-        <v>89.25555448802895</v>
+        <v>98.81894690196053</v>
       </c>
       <c r="F13" t="n">
         <v>89.25555448802895</v>
@@ -5193,49 +5193,49 @@
         <v>300.9166195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="L13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="M13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="N13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="O13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="P13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="Q13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="R13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="S13" t="n">
-        <v>236.7542218096019</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="T13" t="n">
-        <v>251.5799009684067</v>
+        <v>315.7422987473391</v>
       </c>
       <c r="U13" t="n">
-        <v>324.8810936066934</v>
+        <v>389.0434913856257</v>
       </c>
       <c r="V13" t="n">
-        <v>350.4524864926393</v>
+        <v>414.6148842715717</v>
       </c>
       <c r="W13" t="n">
-        <v>349.065809887882</v>
+        <v>413.2282076668144</v>
       </c>
       <c r="X13" t="n">
-        <v>349.065809887882</v>
+        <v>390.5578587475138</v>
       </c>
       <c r="Y13" t="n">
-        <v>317.8981503240243</v>
+        <v>327.4615427379559</v>
       </c>
     </row>
     <row r="14">
@@ -5275,13 +5275,13 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1401.330585172569</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M14" t="n">
-        <v>1401.330585172569</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O14" t="n">
         <v>2821.400904947332</v>
@@ -5299,19 +5299,19 @@
         <v>3013.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2674.622475221327</v>
+        <v>2804.150127677669</v>
       </c>
       <c r="U14" t="n">
-        <v>2282.175493301277</v>
+        <v>2401.906393790183</v>
       </c>
       <c r="V14" t="n">
-        <v>2282.175493301277</v>
+        <v>2019.228591601472</v>
       </c>
       <c r="W14" t="n">
-        <v>1890.889153926582</v>
+        <v>1627.942252226778</v>
       </c>
       <c r="X14" t="n">
-        <v>1546.160029218837</v>
+        <v>1283.213127519033</v>
       </c>
       <c r="Y14" t="n">
         <v>1283.213127519033</v>
@@ -5354,13 +5354,13 @@
         <v>411.8842142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>683.2346758324475</v>
+        <v>931.7246758324475</v>
       </c>
       <c r="M15" t="n">
-        <v>1017.805217575307</v>
+        <v>1266.295217575307</v>
       </c>
       <c r="N15" t="n">
-        <v>1315.621810789732</v>
+        <v>1399.575502182875</v>
       </c>
       <c r="O15" t="n">
         <v>1803.15426247345</v>
@@ -5445,13 +5445,13 @@
         <v>599.1197446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>599.1197446017254</v>
+        <v>544.8356226521192</v>
       </c>
       <c r="Q16" t="n">
-        <v>599.1197446017254</v>
+        <v>65.2</v>
       </c>
       <c r="R16" t="n">
-        <v>177.6984643463186</v>
+        <v>65.2</v>
       </c>
       <c r="S16" t="n">
         <v>65.2</v>
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C17" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D17" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E17" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F17" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G17" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H17" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I17" t="n">
         <v>65.2</v>
       </c>
       <c r="J17" t="n">
-        <v>180.775390095766</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>890.4817564436344</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1697.331756443634</v>
+        <v>1263.359113037656</v>
       </c>
       <c r="M17" t="n">
-        <v>2208.180585172569</v>
+        <v>1774.207941766591</v>
       </c>
       <c r="N17" t="n">
-        <v>2821.400904947332</v>
+        <v>2387.428261541354</v>
       </c>
       <c r="O17" t="n">
-        <v>2821.400904947332</v>
+        <v>3194.278261541354</v>
       </c>
       <c r="P17" t="n">
-        <v>2821.400904947332</v>
+        <v>3194.278261541354</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
       </c>
       <c r="R17" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S17" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T17" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U17" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W17" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X17" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y17" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="18">
@@ -5585,22 +5585,22 @@
         <v>126.454877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>250.4113981428639</v>
+        <v>404.5252825072959</v>
       </c>
       <c r="K18" t="n">
-        <v>439.6042142372473</v>
+        <v>869.9280986016793</v>
       </c>
       <c r="L18" t="n">
-        <v>710.9546758324475</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M18" t="n">
-        <v>797.0352175753068</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N18" t="n">
-        <v>930.3155021828751</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O18" t="n">
-        <v>1323.471838231026</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P18" t="n">
         <v>1712.211182700533</v>
@@ -5685,7 +5685,7 @@
         <v>859.3827230120968</v>
       </c>
       <c r="Q19" t="n">
-        <v>408.0299286428058</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R19" t="n">
         <v>65.2</v>
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C20" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D20" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E20" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F20" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G20" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H20" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I20" t="n">
         <v>65.2</v>
@@ -5749,19 +5749,19 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>1166.215479385524</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>1677.064308114459</v>
+        <v>2483.914308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>2290.284627889223</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>2821.400904947332</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="P20" t="n">
-        <v>2821.400904947332</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="Q20" t="n">
         <v>3260</v>
@@ -5770,25 +5770,25 @@
         <v>3260</v>
       </c>
       <c r="S20" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V20" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W20" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y20" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="21">
@@ -5825,19 +5825,19 @@
         <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>439.6042142372473</v>
+        <v>715.8142142372474</v>
       </c>
       <c r="L21" t="n">
-        <v>710.9546758324475</v>
+        <v>987.1646758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>797.0352175753068</v>
+        <v>1073.245217575307</v>
       </c>
       <c r="N21" t="n">
-        <v>930.3155021828751</v>
+        <v>1206.525502182875</v>
       </c>
       <c r="O21" t="n">
-        <v>1323.471838231026</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.211182700533</v>
@@ -5922,10 +5922,10 @@
         <v>859.3827230120968</v>
       </c>
       <c r="Q22" t="n">
-        <v>601.5389976606127</v>
+        <v>408.0299286428058</v>
       </c>
       <c r="R22" t="n">
-        <v>149.4156360634904</v>
+        <v>65.2</v>
       </c>
       <c r="S22" t="n">
         <v>65.2</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C23" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D23" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E23" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F23" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G23" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H23" t="n">
         <v>65.2</v>
@@ -5980,52 +5980,52 @@
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>456.5091130376557</v>
+        <v>180.775390095766</v>
       </c>
       <c r="K23" t="n">
-        <v>1166.215479385524</v>
+        <v>890.4817564436344</v>
       </c>
       <c r="L23" t="n">
-        <v>1973.065479385524</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M23" t="n">
-        <v>2483.914308114459</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O23" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P23" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>3260</v>
       </c>
       <c r="R23" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S23" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T23" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6059,22 +6059,22 @@
         <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>250.4113981428639</v>
+        <v>404.5252825072959</v>
       </c>
       <c r="K24" t="n">
-        <v>439.6042142372473</v>
+        <v>593.7180986016792</v>
       </c>
       <c r="L24" t="n">
-        <v>710.9546758324475</v>
+        <v>865.0685601968793</v>
       </c>
       <c r="M24" t="n">
-        <v>797.0352175753068</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N24" t="n">
-        <v>930.3155021828751</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1445.567953866594</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P24" t="n">
         <v>1712.211182700533</v>
@@ -6156,13 +6156,13 @@
         <v>859.3827230120968</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3827230120968</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q25" t="n">
-        <v>601.5389976606127</v>
+        <v>65.2</v>
       </c>
       <c r="R25" t="n">
-        <v>149.4156360634904</v>
+        <v>65.2</v>
       </c>
       <c r="S25" t="n">
         <v>65.2</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>681.6712852464632</v>
+        <v>1028.042761166565</v>
       </c>
       <c r="C26" t="n">
-        <v>454.9292870212168</v>
+        <v>801.3007629413187</v>
       </c>
       <c r="D26" t="n">
-        <v>267.718018597126</v>
+        <v>614.089494517228</v>
       </c>
       <c r="E26" t="n">
-        <v>246.6982411146742</v>
+        <v>432.9144545102899</v>
       </c>
       <c r="F26" t="n">
-        <v>246.6982411146742</v>
+        <v>251.2077588456315</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>246.5382411146742</v>
       </c>
       <c r="H26" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I26" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J26" t="n">
-        <v>61.84</v>
+        <v>452.9891130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.695479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1536.816366347868</v>
+        <v>1162.695479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>1536.816366347868</v>
+        <v>1673.544308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1888.130904947332</v>
+        <v>2286.764627889223</v>
       </c>
       <c r="O26" t="n">
-        <v>1888.130904947332</v>
+        <v>2286.764627889223</v>
       </c>
       <c r="P26" t="n">
-        <v>2653.400904947332</v>
+        <v>3050.054627889226</v>
       </c>
       <c r="Q26" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R26" t="n">
-        <v>3065.860001183541</v>
+        <v>3057.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>2785.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>2785.286094312508</v>
       </c>
       <c r="U26" t="n">
-        <v>2427.957223879615</v>
+        <v>2356.779734162396</v>
       </c>
       <c r="V26" t="n">
-        <v>2019.016795428278</v>
+        <v>1947.839305711059</v>
       </c>
       <c r="W26" t="n">
-        <v>1601.467829790957</v>
+        <v>1947.839305711059</v>
       </c>
       <c r="X26" t="n">
-        <v>1230.476078820585</v>
+        <v>1576.847554740687</v>
       </c>
       <c r="Y26" t="n">
-        <v>941.2665508581547</v>
+        <v>1287.638026778257</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>768.1567292570302</v>
+        <v>767.9967292570302</v>
       </c>
       <c r="C27" t="n">
-        <v>630.6820702211521</v>
+        <v>630.5220702211521</v>
       </c>
       <c r="D27" t="n">
-        <v>506.502588506301</v>
+        <v>506.342588506301</v>
       </c>
       <c r="E27" t="n">
-        <v>387.6418842417428</v>
+        <v>387.4818842417428</v>
       </c>
       <c r="F27" t="n">
-        <v>271.8477000620692</v>
+        <v>271.6877000620692</v>
       </c>
       <c r="G27" t="n">
-        <v>170.0905931175971</v>
+        <v>169.9305931175971</v>
       </c>
       <c r="H27" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I27" t="n">
-        <v>69.63487796756496</v>
+        <v>69.47487796756495</v>
       </c>
       <c r="J27" t="n">
-        <v>416.3413981428639</v>
+        <v>416.1813981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>828.2842142372474</v>
+        <v>828.1242142372473</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.224675832447</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.055217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.085502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.213656412845</v>
+        <v>2448.877953866594</v>
       </c>
       <c r="P27" t="n">
-        <v>2580.493000882351</v>
+        <v>2580.333000882351</v>
       </c>
       <c r="Q27" t="n">
-        <v>2631.894528442776</v>
+        <v>2631.734528442777</v>
       </c>
       <c r="R27" t="n">
-        <v>2306.365440268656</v>
+        <v>2306.205440268656</v>
       </c>
       <c r="S27" t="n">
-        <v>2062.361399900361</v>
+        <v>2062.201399900362</v>
       </c>
       <c r="T27" t="n">
-        <v>1880.18183907459</v>
+        <v>1880.02183907459</v>
       </c>
       <c r="U27" t="n">
-        <v>1703.201677700664</v>
+        <v>1703.041677700664</v>
       </c>
       <c r="V27" t="n">
-        <v>1511.776761345593</v>
+        <v>1511.616761345593</v>
       </c>
       <c r="W27" t="n">
-        <v>1302.308940224554</v>
+        <v>1302.148940224554</v>
       </c>
       <c r="X27" t="n">
-        <v>1105.477890279718</v>
+        <v>1105.317890279718</v>
       </c>
       <c r="Y27" t="n">
-        <v>929.3249682937237</v>
+        <v>929.1649682937237</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="C28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="D28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="E28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="F28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="G28" t="n">
-        <v>174.1515880782802</v>
+        <v>88.58002669728401</v>
       </c>
       <c r="H28" t="n">
-        <v>170.342369793817</v>
+        <v>84.77080841282076</v>
       </c>
       <c r="I28" t="n">
-        <v>218.2252487298999</v>
+        <v>132.6536873489037</v>
       </c>
       <c r="J28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="K28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="L28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="M28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="N28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="O28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="P28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="Q28" t="n">
-        <v>406.0589893823512</v>
+        <v>320.487428001355</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>200.4410906089449</v>
       </c>
       <c r="S28" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T28" t="n">
-        <v>76.66567915880486</v>
+        <v>76.50567915880487</v>
       </c>
       <c r="U28" t="n">
-        <v>149.9668717970915</v>
+        <v>149.8068717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>175.5382646830375</v>
+        <v>175.3782646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>174.1515880782802</v>
+        <v>173.9915880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>174.1515880782802</v>
+        <v>151.3212391589796</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.1515880782802</v>
+        <v>151.3212391589796</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>434.9831069145334</v>
+        <v>463.3467432781695</v>
       </c>
       <c r="C29" t="n">
-        <v>434.9831069145334</v>
+        <v>260.8471692953474</v>
       </c>
       <c r="D29" t="n">
-        <v>434.9831069145334</v>
+        <v>97.87832511368092</v>
       </c>
       <c r="E29" t="n">
-        <v>274.0100871096155</v>
+        <v>61.68</v>
       </c>
       <c r="F29" t="n">
-        <v>112.5054116469773</v>
+        <v>61.68</v>
       </c>
       <c r="G29" t="n">
-        <v>112.5054116469773</v>
+        <v>61.68</v>
       </c>
       <c r="H29" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I29" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.68</v>
       </c>
       <c r="K29" t="n">
-        <v>1162.855479385524</v>
+        <v>771.3863663478684</v>
       </c>
       <c r="L29" t="n">
-        <v>1928.125479385524</v>
+        <v>1521.331756443634</v>
       </c>
       <c r="M29" t="n">
-        <v>2040.180585172569</v>
+        <v>2032.180585172569</v>
       </c>
       <c r="N29" t="n">
-        <v>2653.400904947332</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>2653.400904947332</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="Q29" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R29" t="n">
-        <v>3086.062021385561</v>
+        <v>3082.102425425965</v>
       </c>
       <c r="S29" t="n">
-        <v>2833.690134716549</v>
+        <v>2833.770942797356</v>
       </c>
       <c r="T29" t="n">
-        <v>2488.563284485676</v>
+        <v>2492.684496606887</v>
       </c>
       <c r="U29" t="n">
-        <v>2080.258944537584</v>
+        <v>2088.4205606992</v>
       </c>
       <c r="V29" t="n">
-        <v>1691.520536288267</v>
+        <v>1703.722556490287</v>
       </c>
       <c r="W29" t="n">
-        <v>1294.173590852967</v>
+        <v>1310.41601509539</v>
       </c>
       <c r="X29" t="n">
-        <v>943.3838600846152</v>
+        <v>963.6666883674432</v>
       </c>
       <c r="Y29" t="n">
-        <v>674.3763523242046</v>
+        <v>698.6995846474367</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>646.9446080449089</v>
+        <v>622.5421838024847</v>
       </c>
       <c r="C30" t="n">
-        <v>529.6719692110511</v>
+        <v>509.3099490090309</v>
       </c>
       <c r="D30" t="n">
-        <v>425.6945076982201</v>
+        <v>409.372891536604</v>
       </c>
       <c r="E30" t="n">
-        <v>327.0358236356822</v>
+        <v>314.7546115144701</v>
       </c>
       <c r="F30" t="n">
-        <v>231.4436596580288</v>
+        <v>223.2028515772207</v>
       </c>
       <c r="G30" t="n">
-        <v>149.8885729155769</v>
+        <v>145.6881688751729</v>
       </c>
       <c r="H30" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I30" t="n">
-        <v>89.43487796756496</v>
+        <v>61.68</v>
       </c>
       <c r="J30" t="n">
-        <v>455.9413981428639</v>
+        <v>185.636520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>887.6842142372473</v>
+        <v>374.8293362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>1401.584675832447</v>
+        <v>882.4740147423339</v>
       </c>
       <c r="M30" t="n">
-        <v>1730.215217575307</v>
+        <v>968.5545564851932</v>
       </c>
       <c r="N30" t="n">
-        <v>1863.495502182875</v>
+        <v>1348.344841092761</v>
       </c>
       <c r="O30" t="n">
-        <v>2102.537953866594</v>
+        <v>1833.897292776481</v>
       </c>
       <c r="P30" t="n">
-        <v>2257.662697852048</v>
+        <v>2192.936637245987</v>
       </c>
       <c r="Q30" t="n">
-        <v>2328.864225412473</v>
+        <v>2268.098164806413</v>
       </c>
       <c r="R30" t="n">
-        <v>2023.537157440373</v>
+        <v>1966.811500874716</v>
       </c>
       <c r="S30" t="n">
-        <v>1799.735137274099</v>
+        <v>1747.049884748846</v>
       </c>
       <c r="T30" t="n">
-        <v>1637.757596650347</v>
+        <v>1589.112748165499</v>
       </c>
       <c r="U30" t="n">
-        <v>1480.979455478441</v>
+        <v>1436.375011033997</v>
       </c>
       <c r="V30" t="n">
-        <v>1309.756559325391</v>
+        <v>1269.19251892135</v>
       </c>
       <c r="W30" t="n">
-        <v>1120.490758406372</v>
+        <v>1083.967122042736</v>
       </c>
       <c r="X30" t="n">
-        <v>943.8617286635564</v>
+        <v>911.3784963403241</v>
       </c>
       <c r="Y30" t="n">
-        <v>787.9108268795823</v>
+        <v>759.467998596754</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>250.9108542254345</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="C31" t="n">
-        <v>222.905554580945</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="D31" t="n">
-        <v>181.9598797773536</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="E31" t="n">
-        <v>145.6155314571954</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="F31" t="n">
-        <v>115.9358789645268</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="G31" t="n">
-        <v>115.9358789645268</v>
+        <v>274.5165398537937</v>
       </c>
       <c r="H31" t="n">
-        <v>132.0024641239244</v>
+        <v>294.5431250131912</v>
       </c>
       <c r="I31" t="n">
-        <v>199.6853430600073</v>
+        <v>366.1860039492742</v>
       </c>
       <c r="J31" t="n">
-        <v>407.3190837124586</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="K31" t="n">
-        <v>363.3587061355464</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="L31" t="n">
-        <v>340.2557690934848</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="M31" t="n">
-        <v>61.84</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="N31" t="n">
-        <v>61.84</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="O31" t="n">
-        <v>61.84</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="P31" t="n">
-        <v>61.84</v>
+        <v>577.7797446017255</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.84</v>
+        <v>96.12391992940428</v>
       </c>
       <c r="R31" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="S31" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T31" t="n">
-        <v>96.46567915880487</v>
+        <v>100.2656791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>189.5668717970915</v>
+        <v>197.3268717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>234.9382646830375</v>
+        <v>246.6582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>253.3791829427149</v>
+        <v>269.0591829427149</v>
       </c>
       <c r="X31" t="n">
-        <v>250.9108542254345</v>
+        <v>270.5999739669084</v>
       </c>
       <c r="Y31" t="n">
-        <v>250.9108542254345</v>
+        <v>270.5999739669084</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>810.1568518063311</v>
+        <v>809.9968518063311</v>
       </c>
       <c r="C32" t="n">
-        <v>649.0714192376504</v>
+        <v>648.9114192376503</v>
       </c>
       <c r="D32" t="n">
-        <v>527.5167164701254</v>
+        <v>527.3567164701253</v>
       </c>
       <c r="E32" t="n">
-        <v>411.9982421197531</v>
+        <v>411.838242119753</v>
       </c>
       <c r="F32" t="n">
-        <v>295.9481121116602</v>
+        <v>295.7881121116602</v>
       </c>
       <c r="G32" t="n">
-        <v>181.0416754581085</v>
+        <v>180.8816754581085</v>
       </c>
       <c r="H32" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I32" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637035</v>
+        <v>445.4363942839051</v>
       </c>
       <c r="K32" t="n">
-        <v>800.8946085891271</v>
+        <v>429.9385154960262</v>
       </c>
       <c r="L32" t="n">
-        <v>794.7697740169842</v>
+        <v>414.4406367081473</v>
       </c>
       <c r="M32" t="n">
-        <v>1300.452822408919</v>
+        <v>513.9827478490324</v>
       </c>
       <c r="N32" t="n">
-        <v>1910.585917781598</v>
+        <v>1124.156045241914</v>
       </c>
       <c r="O32" t="n">
-        <v>2675.8559177816</v>
+        <v>1887.446045241927</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533244</v>
+        <v>2650.736045241939</v>
       </c>
       <c r="Q32" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R32" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="S32" t="n">
-        <v>2885.082658785532</v>
+        <v>2877.082658785532</v>
       </c>
       <c r="T32" t="n">
-        <v>2585.410354009205</v>
+        <v>2577.410354009205</v>
       </c>
       <c r="U32" t="n">
-        <v>2222.560559515659</v>
+        <v>2214.560559515659</v>
       </c>
       <c r="V32" t="n">
-        <v>1884.876099361883</v>
+        <v>1871.276696720887</v>
       </c>
       <c r="W32" t="n">
-        <v>1532.983699381128</v>
+        <v>1532.823699381128</v>
       </c>
       <c r="X32" t="n">
-        <v>1227.648514067322</v>
+        <v>1227.488514067322</v>
       </c>
       <c r="Y32" t="n">
-        <v>1004.095551761457</v>
+        <v>1003.935551761457</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>374.2173353176363</v>
+        <v>374.0573353176363</v>
       </c>
       <c r="C33" t="n">
-        <v>302.3992419383239</v>
+        <v>302.2392419383239</v>
       </c>
       <c r="D33" t="n">
-        <v>243.8763258800384</v>
+        <v>243.7163258800384</v>
       </c>
       <c r="E33" t="n">
-        <v>190.6721872720458</v>
+        <v>190.5121872720458</v>
       </c>
       <c r="F33" t="n">
-        <v>140.5345687489379</v>
+        <v>140.3745687489379</v>
       </c>
       <c r="G33" t="n">
-        <v>104.4340274610315</v>
+        <v>104.2740274610315</v>
       </c>
       <c r="H33" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I33" t="n">
-        <v>88.76209566533032</v>
+        <v>133.824877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>212.7186158406293</v>
+        <v>257.7813981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>401.9114319350127</v>
+        <v>446.9742142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>673.2618935302128</v>
+        <v>718.3246758324474</v>
       </c>
       <c r="M33" t="n">
-        <v>759.3424352730721</v>
+        <v>804.4052175753067</v>
       </c>
       <c r="N33" t="n">
-        <v>892.6227198806404</v>
+        <v>937.685502182875</v>
       </c>
       <c r="O33" t="n">
-        <v>1131.665171564359</v>
+        <v>1176.727953866594</v>
       </c>
       <c r="P33" t="n">
-        <v>1531.294516033866</v>
+        <v>1531.134516033866</v>
       </c>
       <c r="Q33" t="n">
-        <v>1647.046043594291</v>
+        <v>1646.886043594291</v>
       </c>
       <c r="R33" t="n">
-        <v>1387.173521076736</v>
+        <v>1387.013521076736</v>
       </c>
       <c r="S33" t="n">
-        <v>1208.826046365008</v>
+        <v>1208.666046365008</v>
       </c>
       <c r="T33" t="n">
-        <v>1092.303051195802</v>
+        <v>1092.143051195802</v>
       </c>
       <c r="U33" t="n">
-        <v>980.9794554784414</v>
+        <v>980.8194554784415</v>
       </c>
       <c r="V33" t="n">
-        <v>855.2111047799362</v>
+        <v>855.0511047799363</v>
       </c>
       <c r="W33" t="n">
-        <v>711.399849315463</v>
+        <v>711.2398493154631</v>
       </c>
       <c r="X33" t="n">
-        <v>580.2253650271928</v>
+        <v>580.0653650271928</v>
       </c>
       <c r="Y33" t="n">
-        <v>469.7290086977642</v>
+        <v>469.5690086977642</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>479.0766123122328</v>
+        <v>478.9166123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>496.1786181306686</v>
+        <v>496.0186181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>500.5977622556687</v>
+        <v>500.4377622556686</v>
       </c>
       <c r="E34" t="n">
-        <v>509.5266664670817</v>
+        <v>509.3666664670816</v>
       </c>
       <c r="F34" t="n">
-        <v>524.9876390590172</v>
+        <v>524.8276390590171</v>
       </c>
       <c r="G34" t="n">
-        <v>569.4942049459024</v>
+        <v>569.3342049459023</v>
       </c>
       <c r="H34" t="n">
-        <v>630.1107901053</v>
+        <v>629.9507901052999</v>
       </c>
       <c r="I34" t="n">
-        <v>742.3436690413829</v>
+        <v>742.1836690413828</v>
       </c>
       <c r="J34" t="n">
-        <v>994.5274096938342</v>
+        <v>994.3674096938341</v>
       </c>
       <c r="K34" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="L34" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="M34" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="N34" t="n">
-        <v>817.287940815447</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="O34" t="n">
-        <v>463.3025225538156</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="P34" t="n">
-        <v>61.84</v>
+        <v>942.933933744191</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>502.6922504860112</v>
       </c>
       <c r="R34" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="S34" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T34" t="n">
-        <v>141.0156791588049</v>
+        <v>140.8556791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>278.6668717970915</v>
+        <v>278.5068717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>368.5882646830375</v>
+        <v>368.4282646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>431.5791829427149</v>
+        <v>431.4191829427149</v>
       </c>
       <c r="X34" t="n">
-        <v>473.7099739669084</v>
+        <v>473.5499739669084</v>
       </c>
       <c r="Y34" t="n">
-        <v>476.2192746459407</v>
+        <v>476.0592746459407</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>810.1568518063311</v>
+        <v>796.5574491653355</v>
       </c>
       <c r="C35" t="n">
-        <v>649.0714192376504</v>
+        <v>635.4720165966547</v>
       </c>
       <c r="D35" t="n">
-        <v>527.5167164701254</v>
+        <v>513.9173138291296</v>
       </c>
       <c r="E35" t="n">
-        <v>411.9982421197531</v>
+        <v>398.3988394787573</v>
       </c>
       <c r="F35" t="n">
-        <v>295.9481121116602</v>
+        <v>295.7881121116602</v>
       </c>
       <c r="G35" t="n">
-        <v>181.0416754581085</v>
+        <v>180.8816754581085</v>
       </c>
       <c r="H35" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I35" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J35" t="n">
-        <v>445.5561922637035</v>
+        <v>94.21681311122893</v>
       </c>
       <c r="K35" t="n">
-        <v>1155.262558611572</v>
+        <v>803.9231794590974</v>
       </c>
       <c r="L35" t="n">
-        <v>1148.01532740662</v>
+        <v>788.5889659361592</v>
       </c>
       <c r="M35" t="n">
-        <v>1132.477246598539</v>
+        <v>1294.312216348295</v>
       </c>
       <c r="N35" t="n">
-        <v>1742.610341971219</v>
+        <v>1904.485513741176</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533243</v>
+        <v>2667.775513741196</v>
       </c>
       <c r="P35" t="n">
-        <v>2660.033647533244</v>
+        <v>2651.993445513042</v>
       </c>
       <c r="Q35" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R35" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="S35" t="n">
-        <v>2885.082658785532</v>
+        <v>2877.082658785532</v>
       </c>
       <c r="T35" t="n">
-        <v>2585.410354009205</v>
+        <v>2577.410354009205</v>
       </c>
       <c r="U35" t="n">
-        <v>2222.560559515659</v>
+        <v>2214.560559515659</v>
       </c>
       <c r="V35" t="n">
-        <v>1879.276696720887</v>
+        <v>1871.276696720887</v>
       </c>
       <c r="W35" t="n">
-        <v>1527.384296740132</v>
+        <v>1519.384296740132</v>
       </c>
       <c r="X35" t="n">
-        <v>1222.049111426326</v>
+        <v>1214.049111426326</v>
       </c>
       <c r="Y35" t="n">
-        <v>998.4961491204613</v>
+        <v>990.4961491204613</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>374.2173353176363</v>
+        <v>374.0573353176363</v>
       </c>
       <c r="C36" t="n">
-        <v>302.3992419383239</v>
+        <v>302.2392419383239</v>
       </c>
       <c r="D36" t="n">
-        <v>243.8763258800384</v>
+        <v>243.7163258800384</v>
       </c>
       <c r="E36" t="n">
-        <v>190.6721872720458</v>
+        <v>190.5121872720458</v>
       </c>
       <c r="F36" t="n">
-        <v>140.5345687489379</v>
+        <v>140.3745687489379</v>
       </c>
       <c r="G36" t="n">
-        <v>104.4340274610315</v>
+        <v>104.2740274610315</v>
       </c>
       <c r="H36" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I36" t="n">
-        <v>133.984877967565</v>
+        <v>133.824877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>257.9413981428639</v>
+        <v>257.7813981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>447.1342142372473</v>
+        <v>446.9742142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>960.3618935302128</v>
+        <v>718.3246758324474</v>
       </c>
       <c r="M36" t="n">
-        <v>1046.442435273072</v>
+        <v>1046.282435273072</v>
       </c>
       <c r="N36" t="n">
-        <v>1179.72271988064</v>
+        <v>1179.56271988064</v>
       </c>
       <c r="O36" t="n">
-        <v>1418.765171564359</v>
+        <v>1418.605171564359</v>
       </c>
       <c r="P36" t="n">
-        <v>1531.294516033866</v>
+        <v>1531.134516033866</v>
       </c>
       <c r="Q36" t="n">
-        <v>1647.046043594291</v>
+        <v>1646.886043594291</v>
       </c>
       <c r="R36" t="n">
-        <v>1387.173521076736</v>
+        <v>1387.013521076736</v>
       </c>
       <c r="S36" t="n">
-        <v>1208.826046365008</v>
+        <v>1208.666046365008</v>
       </c>
       <c r="T36" t="n">
-        <v>1092.303051195802</v>
+        <v>1092.143051195802</v>
       </c>
       <c r="U36" t="n">
-        <v>980.9794554784414</v>
+        <v>980.8194554784415</v>
       </c>
       <c r="V36" t="n">
-        <v>855.2111047799362</v>
+        <v>855.0511047799363</v>
       </c>
       <c r="W36" t="n">
-        <v>711.399849315463</v>
+        <v>711.2398493154631</v>
       </c>
       <c r="X36" t="n">
-        <v>580.2253650271928</v>
+        <v>580.0653650271928</v>
       </c>
       <c r="Y36" t="n">
-        <v>469.7290086977642</v>
+        <v>469.5690086977642</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>479.0766123122328</v>
+        <v>478.9166123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>496.1786181306686</v>
+        <v>496.0186181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>500.5977622556687</v>
+        <v>500.4377622556686</v>
       </c>
       <c r="E37" t="n">
-        <v>509.5266664670817</v>
+        <v>509.3666664670816</v>
       </c>
       <c r="F37" t="n">
-        <v>524.9876390590172</v>
+        <v>524.8276390590171</v>
       </c>
       <c r="G37" t="n">
-        <v>569.4942049459024</v>
+        <v>569.3342049459023</v>
       </c>
       <c r="H37" t="n">
-        <v>630.1107901053</v>
+        <v>629.9507901052999</v>
       </c>
       <c r="I37" t="n">
-        <v>742.3436690413829</v>
+        <v>742.1836690413828</v>
       </c>
       <c r="J37" t="n">
-        <v>994.5274096938342</v>
+        <v>994.3674096938341</v>
       </c>
       <c r="K37" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="L37" t="n">
-        <v>995.9918436307026</v>
+        <v>980.1290747500124</v>
       </c>
       <c r="M37" t="n">
-        <v>995.9918436307026</v>
+        <v>747.1678511110731</v>
       </c>
       <c r="N37" t="n">
-        <v>995.9918436307026</v>
+        <v>463.1425225538156</v>
       </c>
       <c r="O37" t="n">
-        <v>903.5442058119954</v>
+        <v>463.1425225538156</v>
       </c>
       <c r="P37" t="n">
-        <v>502.0816832581799</v>
+        <v>61.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="R37" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="S37" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T37" t="n">
-        <v>141.0156791588049</v>
+        <v>140.8556791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>278.6668717970915</v>
+        <v>278.5068717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>368.5882646830375</v>
+        <v>368.4282646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>431.5791829427149</v>
+        <v>431.4191829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>473.7099739669084</v>
+        <v>473.5499739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>476.2192746459407</v>
+        <v>476.0592746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>804.5574491653355</v>
+        <v>809.9968518063311</v>
       </c>
       <c r="C38" t="n">
-        <v>643.4720165966547</v>
+        <v>648.9114192376503</v>
       </c>
       <c r="D38" t="n">
-        <v>521.9173138291296</v>
+        <v>527.3567164701253</v>
       </c>
       <c r="E38" t="n">
-        <v>406.3988394787573</v>
+        <v>411.838242119753</v>
       </c>
       <c r="F38" t="n">
-        <v>290.3487094706645</v>
+        <v>295.7881121116602</v>
       </c>
       <c r="G38" t="n">
-        <v>181.0416754581085</v>
+        <v>180.8816754581085</v>
       </c>
       <c r="H38" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I38" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J38" t="n">
-        <v>445.5561922637035</v>
+        <v>445.4363942839049</v>
       </c>
       <c r="K38" t="n">
-        <v>430.0181114556225</v>
+        <v>1155.142760631773</v>
       </c>
       <c r="L38" t="n">
-        <v>731.38971920916</v>
+        <v>1139.814317305614</v>
       </c>
       <c r="M38" t="n">
-        <v>1237.072767601094</v>
+        <v>1645.53756771775</v>
       </c>
       <c r="N38" t="n">
-        <v>1847.205862973774</v>
+        <v>2255.710865110631</v>
       </c>
       <c r="O38" t="n">
-        <v>2612.475862973775</v>
+        <v>2240.212986322752</v>
       </c>
       <c r="P38" t="n">
-        <v>2660.033647533244</v>
+        <v>3003.502986322779</v>
       </c>
       <c r="Q38" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="S38" t="n">
-        <v>2885.082658785532</v>
+        <v>2877.082658785532</v>
       </c>
       <c r="T38" t="n">
-        <v>2585.410354009205</v>
+        <v>2577.410354009205</v>
       </c>
       <c r="U38" t="n">
-        <v>2222.560559515659</v>
+        <v>2214.560559515659</v>
       </c>
       <c r="V38" t="n">
-        <v>1879.276696720887</v>
+        <v>1871.276696720887</v>
       </c>
       <c r="W38" t="n">
-        <v>1527.384296740132</v>
+        <v>1519.384296740132</v>
       </c>
       <c r="X38" t="n">
-        <v>1222.049111426326</v>
+        <v>1214.049111426326</v>
       </c>
       <c r="Y38" t="n">
-        <v>998.4961491204613</v>
+        <v>1003.935551761457</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>374.2173353176363</v>
+        <v>374.0573353176363</v>
       </c>
       <c r="C39" t="n">
-        <v>302.3992419383239</v>
+        <v>302.2392419383239</v>
       </c>
       <c r="D39" t="n">
-        <v>243.8763258800384</v>
+        <v>243.7163258800384</v>
       </c>
       <c r="E39" t="n">
-        <v>190.6721872720458</v>
+        <v>190.5121872720458</v>
       </c>
       <c r="F39" t="n">
-        <v>140.5345687489379</v>
+        <v>140.3745687489379</v>
       </c>
       <c r="G39" t="n">
-        <v>104.4340274610315</v>
+        <v>104.2740274610315</v>
       </c>
       <c r="H39" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I39" t="n">
-        <v>133.984877967565</v>
+        <v>133.824877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>545.0413981428638</v>
+        <v>257.7813981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>734.2342142372472</v>
+        <v>446.9742142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>1005.584675832447</v>
+        <v>718.3246758324474</v>
       </c>
       <c r="M39" t="n">
-        <v>1091.665217575307</v>
+        <v>804.4052175753067</v>
       </c>
       <c r="N39" t="n">
-        <v>1295.474247441065</v>
+        <v>937.685502182875</v>
       </c>
       <c r="O39" t="n">
-        <v>1534.516699124785</v>
+        <v>1418.605171564359</v>
       </c>
       <c r="P39" t="n">
-        <v>1647.046043594291</v>
+        <v>1531.134516033866</v>
       </c>
       <c r="Q39" t="n">
-        <v>1647.046043594291</v>
+        <v>1646.886043594291</v>
       </c>
       <c r="R39" t="n">
-        <v>1387.173521076736</v>
+        <v>1387.013521076736</v>
       </c>
       <c r="S39" t="n">
-        <v>1208.826046365008</v>
+        <v>1208.666046365008</v>
       </c>
       <c r="T39" t="n">
-        <v>1092.303051195802</v>
+        <v>1092.143051195802</v>
       </c>
       <c r="U39" t="n">
-        <v>980.9794554784414</v>
+        <v>980.8194554784415</v>
       </c>
       <c r="V39" t="n">
-        <v>855.2111047799362</v>
+        <v>855.0511047799363</v>
       </c>
       <c r="W39" t="n">
-        <v>711.399849315463</v>
+        <v>711.2398493154631</v>
       </c>
       <c r="X39" t="n">
-        <v>580.2253650271928</v>
+        <v>580.0653650271928</v>
       </c>
       <c r="Y39" t="n">
-        <v>469.7290086977642</v>
+        <v>469.5690086977642</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>479.0766123122328</v>
+        <v>478.9166123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>496.1786181306686</v>
+        <v>496.0186181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>500.5977622556687</v>
+        <v>500.4377622556686</v>
       </c>
       <c r="E40" t="n">
-        <v>509.5266664670817</v>
+        <v>509.3666664670816</v>
       </c>
       <c r="F40" t="n">
-        <v>524.9876390590172</v>
+        <v>524.8276390590171</v>
       </c>
       <c r="G40" t="n">
-        <v>569.4942049459024</v>
+        <v>569.3342049459023</v>
       </c>
       <c r="H40" t="n">
-        <v>630.1107901053</v>
+        <v>629.9507901052999</v>
       </c>
       <c r="I40" t="n">
-        <v>742.3436690413829</v>
+        <v>742.1836690413828</v>
       </c>
       <c r="J40" t="n">
-        <v>994.5274096938342</v>
+        <v>994.3674096938341</v>
       </c>
       <c r="K40" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="L40" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="M40" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="N40" t="n">
-        <v>995.9918436307026</v>
+        <v>995.8318436307026</v>
       </c>
       <c r="O40" t="n">
-        <v>642.0064253690714</v>
+        <v>641.8464253690713</v>
       </c>
       <c r="P40" t="n">
-        <v>642.0064253690714</v>
+        <v>240.3839028152557</v>
       </c>
       <c r="Q40" t="n">
-        <v>201.7647421108916</v>
+        <v>61.68</v>
       </c>
       <c r="R40" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="S40" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T40" t="n">
-        <v>141.0156791588049</v>
+        <v>140.8556791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>278.6668717970915</v>
+        <v>278.5068717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>368.5882646830375</v>
+        <v>368.4282646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>431.5791829427149</v>
+        <v>431.4191829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>473.7099739669084</v>
+        <v>473.5499739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>476.2192746459407</v>
+        <v>476.0592746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1301.065942715422</v>
+        <v>1294.845336654816</v>
       </c>
       <c r="C41" t="n">
-        <v>1058.162328328559</v>
+        <v>1052.951823278054</v>
       </c>
       <c r="D41" t="n">
-        <v>854.7894437428527</v>
+        <v>850.5890397024486</v>
       </c>
       <c r="E41" t="n">
-        <v>657.4527875742984</v>
+        <v>654.2624845439955</v>
       </c>
       <c r="F41" t="n">
-        <v>459.5844757480239</v>
+        <v>457.4042737278219</v>
       </c>
       <c r="G41" t="n">
-        <v>262.8598572762903</v>
+        <v>261.6897562661893</v>
       </c>
       <c r="H41" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I41" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>452.9891130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.695479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>771.5463663478683</v>
+        <v>1925.985479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>1282.395195076803</v>
+        <v>2436.834308114459</v>
       </c>
       <c r="N41" t="n">
-        <v>1888.130904947331</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>2645.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3042.708486032026</v>
       </c>
       <c r="S41" t="n">
-        <v>3092</v>
+        <v>2754.983064009477</v>
       </c>
       <c r="T41" t="n">
-        <v>2710.509513405491</v>
+        <v>2754.983064009477</v>
       </c>
       <c r="U41" t="n">
-        <v>2710.509513405491</v>
+        <v>2754.983064009477</v>
       </c>
       <c r="V41" t="n">
-        <v>2285.407468792538</v>
+        <v>2330.891120406624</v>
       </c>
       <c r="W41" t="n">
-        <v>1851.696886993601</v>
+        <v>1898.190639617789</v>
       </c>
       <c r="X41" t="n">
-        <v>1464.543519861613</v>
+        <v>1873.953160531968</v>
       </c>
       <c r="Y41" t="n">
-        <v>1464.543519861613</v>
+        <v>1569.592117418023</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>873.334896824049</v>
+        <v>749.1955676573548</v>
       </c>
       <c r="C42" t="n">
-        <v>719.6986216265548</v>
+        <v>596.5693934699615</v>
       </c>
       <c r="D42" t="n">
-        <v>579.3575237500875</v>
+        <v>457.2383966035952</v>
       </c>
       <c r="E42" t="n">
-        <v>444.335203323913</v>
+        <v>323.2261771875218</v>
       </c>
       <c r="F42" t="n">
-        <v>312.3794029826233</v>
+        <v>192.280477856333</v>
       </c>
       <c r="G42" t="n">
-        <v>194.460679876535</v>
+        <v>192.280477856333</v>
       </c>
       <c r="H42" t="n">
-        <v>70.04847059732175</v>
+        <v>68.87836958722075</v>
       </c>
       <c r="I42" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J42" t="n">
-        <v>321.5981283371855</v>
+        <v>393.536520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>717.7009444315688</v>
+        <v>723.841965014759</v>
       </c>
       <c r="L42" t="n">
-        <v>1195.961406026769</v>
+        <v>1203.092426609959</v>
       </c>
       <c r="M42" t="n">
-        <v>1488.951947769628</v>
+        <v>1497.072968352818</v>
       </c>
       <c r="N42" t="n">
-        <v>1829.142232377197</v>
+        <v>1838.253252960387</v>
       </c>
       <c r="O42" t="n">
-        <v>2275.094684060916</v>
+        <v>2285.195704644106</v>
       </c>
       <c r="P42" t="n">
-        <v>2594.534028530422</v>
+        <v>2605.625049113612</v>
       </c>
       <c r="Q42" t="n">
-        <v>2630.095556090847</v>
+        <v>2642.176576674038</v>
       </c>
       <c r="R42" t="n">
-        <v>2315.207099845949</v>
+        <v>2301.495973348402</v>
       </c>
       <c r="S42" t="n">
-        <v>2055.041443316038</v>
+        <v>2042.340417828593</v>
       </c>
       <c r="T42" t="n">
-        <v>1856.70026632865</v>
+        <v>1845.009341851306</v>
       </c>
       <c r="U42" t="n">
-        <v>1663.558488793108</v>
+        <v>1652.877665325865</v>
       </c>
       <c r="V42" t="n">
-        <v>1455.971956276421</v>
+        <v>1446.301233819279</v>
       </c>
       <c r="W42" t="n">
-        <v>1455.971956276421</v>
+        <v>1328.802324079424</v>
       </c>
       <c r="X42" t="n">
-        <v>1242.979290169969</v>
+        <v>1116.819758983073</v>
       </c>
       <c r="Y42" t="n">
-        <v>1050.664752022359</v>
+        <v>925.5153218455634</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="C43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="D43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="E43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="F43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="G43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="H43" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="J43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="K43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="L43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="M43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="N43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="O43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="P43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="Q43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="R43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="S43" t="n">
-        <v>93.88287893608292</v>
+        <v>86.48234695909039</v>
       </c>
       <c r="T43" t="n">
-        <v>92.84796327319634</v>
+        <v>86.45753230630484</v>
       </c>
       <c r="U43" t="n">
-        <v>92.84796327319634</v>
+        <v>86.45753230630484</v>
       </c>
       <c r="V43" t="n">
-        <v>99.35912721245283</v>
+        <v>97.17892519225082</v>
       </c>
       <c r="W43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="X43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
       <c r="Y43" t="n">
-        <v>81.81083444607941</v>
+        <v>80.6407334359784</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1377.434500389448</v>
+        <v>1597.875639685119</v>
       </c>
       <c r="C44" t="n">
-        <v>1088.066239537939</v>
+        <v>1305.477075803307</v>
       </c>
       <c r="D44" t="n">
-        <v>838.2287084875852</v>
+        <v>1052.609241722651</v>
       </c>
       <c r="E44" t="n">
-        <v>796.8467269682379</v>
+        <v>805.777636059147</v>
       </c>
       <c r="F44" t="n">
-        <v>552.5137686773169</v>
+        <v>558.4143747379229</v>
       </c>
       <c r="G44" t="n">
-        <v>309.3245037409368</v>
+        <v>312.1948067712398</v>
       </c>
       <c r="H44" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I44" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J44" t="n">
-        <v>453.1491130376558</v>
+        <v>61.68</v>
       </c>
       <c r="K44" t="n">
-        <v>1162.855479385524</v>
+        <v>771.3863663478684</v>
       </c>
       <c r="L44" t="n">
-        <v>1162.855479385524</v>
+        <v>1534.676366347868</v>
       </c>
       <c r="M44" t="n">
-        <v>1673.704308114459</v>
+        <v>2045.525195076803</v>
       </c>
       <c r="N44" t="n">
-        <v>2286.924627889222</v>
+        <v>2658.745514851566</v>
       </c>
       <c r="O44" t="n">
-        <v>2653.400904947332</v>
+        <v>2658.745514851566</v>
       </c>
       <c r="P44" t="n">
-        <v>2653.400904947332</v>
+        <v>2658.745514851566</v>
       </c>
       <c r="Q44" t="n">
-        <v>3092</v>
+        <v>3084</v>
       </c>
       <c r="R44" t="n">
-        <v>3003.233738557278</v>
+        <v>2992.203435526975</v>
       </c>
       <c r="S44" t="n">
-        <v>3003.233738557278</v>
+        <v>2992.203435526975</v>
       </c>
       <c r="T44" t="n">
-        <v>3003.233738557278</v>
+        <v>2992.203435526975</v>
       </c>
       <c r="U44" t="n">
-        <v>3003.233738557278</v>
+        <v>2498.040509720298</v>
       </c>
       <c r="V44" t="n">
-        <v>2531.667047479678</v>
+        <v>2498.040509720298</v>
       </c>
       <c r="W44" t="n">
-        <v>2051.491819216095</v>
+        <v>2498.040509720298</v>
       </c>
       <c r="X44" t="n">
-        <v>2051.491819216095</v>
+        <v>2277.993564572373</v>
       </c>
       <c r="Y44" t="n">
-        <v>1699.656028627402</v>
+        <v>1923.127470953376</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1198.587422076574</v>
+        <v>820.6152918212238</v>
       </c>
       <c r="C45" t="n">
-        <v>998.4865004144335</v>
+        <v>617.48406712878</v>
       </c>
       <c r="D45" t="n">
-        <v>811.6807560733198</v>
+        <v>427.6480197573632</v>
       </c>
       <c r="E45" t="n">
-        <v>630.1937891824989</v>
+        <v>243.1307498362393</v>
       </c>
       <c r="F45" t="n">
-        <v>451.7733423765627</v>
+        <v>61.68</v>
       </c>
       <c r="G45" t="n">
-        <v>287.3899728058279</v>
+        <v>61.68</v>
       </c>
       <c r="H45" t="n">
-        <v>116.5131170619682</v>
+        <v>61.68</v>
       </c>
       <c r="I45" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J45" t="n">
-        <v>347.166520175299</v>
+        <v>198.3403572352858</v>
       </c>
       <c r="K45" t="n">
-        <v>697.7293362696823</v>
+        <v>545.9331733296692</v>
       </c>
       <c r="L45" t="n">
-        <v>1130.449797864882</v>
+        <v>975.6836349248694</v>
       </c>
       <c r="M45" t="n">
-        <v>1377.900339607742</v>
+        <v>1220.164176667728</v>
       </c>
       <c r="N45" t="n">
-        <v>1672.55062421531</v>
+        <v>1511.844461275297</v>
       </c>
       <c r="O45" t="n">
-        <v>1931.721912959016</v>
+        <v>1909.286912959016</v>
       </c>
       <c r="P45" t="n">
-        <v>2205.621257428522</v>
+        <v>2180.216257428523</v>
       </c>
       <c r="Q45" t="n">
-        <v>2195.440181579553</v>
+        <v>2167.00487854925</v>
       </c>
       <c r="R45" t="n">
-        <v>2195.440181579553</v>
+        <v>2167.00487854925</v>
       </c>
       <c r="S45" t="n">
-        <v>2195.440181579553</v>
+        <v>2167.00487854925</v>
       </c>
       <c r="T45" t="n">
-        <v>1950.634358127519</v>
+        <v>1919.168752066913</v>
       </c>
       <c r="U45" t="n">
-        <v>1711.02793412733</v>
+        <v>1919.168752066913</v>
       </c>
       <c r="V45" t="n">
-        <v>1456.976755145997</v>
+        <v>1662.087270055277</v>
       </c>
       <c r="W45" t="n">
-        <v>1456.976755145997</v>
+        <v>1551.737199758445</v>
       </c>
       <c r="X45" t="n">
-        <v>1456.976755145997</v>
+        <v>1289.249584157043</v>
       </c>
       <c r="Y45" t="n">
-        <v>1422.381923739531</v>
+        <v>1047.440096514483</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="C46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="D46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="E46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="F46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="G46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="H46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="I46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="J46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="K46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="L46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="M46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="N46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="O46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="P46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="R46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="S46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="T46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="U46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="V46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="W46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="X46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
       <c r="Y46" t="n">
-        <v>61.84</v>
+        <v>61.68</v>
       </c>
     </row>
   </sheetData>
@@ -7964,13 +7964,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>165.4169962838683</v>
+        <v>503.2488834659006</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>15.58188507602177</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>815</v>
+        <v>503.2488834658998</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
         <v>815.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>368.571219908533</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>51.26150624509023</v>
       </c>
       <c r="K8" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>783.009300302612</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>1010.856995281693</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>815.2870600406815</v>
+        <v>197.6947560219367</v>
       </c>
       <c r="Q8" t="n">
-        <v>189.0411843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>814.9999999999999</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>186.9906878526441</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8918,16 +8918,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>237.4900058455003</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>151.7858245236418</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>815</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>239.2082787301582</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9392,7 +9392,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>606.7289575115773</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>337.3331612070587</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>151.7858245236418</v>
       </c>
       <c r="K23" t="n">
         <v>716.8751175230994</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>234.7583464536658</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>832.1121283723239</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>773.2870600406818</v>
+        <v>771.2870600406849</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>207.1109389848327</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>773</v>
+        <v>757.5205960563293</v>
       </c>
       <c r="M29" t="n">
-        <v>657.4491031847872</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
@@ -10337,22 +10337,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>367.1677321621693</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>658.1517176717938</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.247869574094</v>
+        <v>841.2478695741054</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>771.2870600406944</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>82.59735122520746</v>
       </c>
       <c r="K35" t="n">
         <v>716.8751175230994</v>
@@ -10580,16 +10580,16 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>236.262342080497</v>
+        <v>841.2478695741127</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600406825</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,10 +10811,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>304.4157654076135</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,13 +10823,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.247869574094</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>62.75196675455613</v>
+        <v>771.287060040709</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>267.8576278679342</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1089.103210464307</v>
+        <v>687.9222882040505</v>
       </c>
       <c r="O41" t="n">
-        <v>843.247869574094</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>770.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,13 +11297,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>440.4259272085471</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>602.3726693259032</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23229,7 +23229,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>57.40845813745594</v>
+        <v>31.52985930916157</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>39.91509747794967</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
         <v>198.5476281577792</v>
@@ -23447,10 +23447,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>31.6093698812432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23514,13 +23514,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>128.2323759317789</v>
       </c>
       <c r="U14" t="n">
-        <v>9.698784447761739</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>378.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -23529,7 +23529,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -23660,16 +23660,16 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>382.7066165981673</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>58.39506052829836</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23900,10 +23900,10 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -24137,13 +24137,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>191.5739783276288</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24371,16 +24371,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>191.5739783276288</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24417,13 +24417,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>158.5537098992413</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>174.1345497333685</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24462,16 +24462,16 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>47.72524664804467</v>
@@ -24614,10 +24614,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>160.8253284926234</v>
+        <v>382.7562539626651</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,7 +24632,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>62.46535284946236</v>
@@ -24648,22 +24648,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>204.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>165.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>119.5269477443245</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>155.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>158.7573722870162</v>
+        <v>154.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>112.8509011730199</v>
+        <v>159.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24803,22 +24803,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42.11380033707866</v>
+        <v>38.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>23.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>36.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>31.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>25.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04387284153003179</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,31 +24830,31 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>39.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>155.6757204861382</v>
+        <v>174.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>271.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>326.1850752716849</v>
+        <v>322.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>395.445564079015</v>
+        <v>391.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>442.4478973282775</v>
+        <v>438.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>480.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>481.6021279811511</v>
+        <v>443.5026472510408</v>
       </c>
       <c r="S31" t="n">
-        <v>117.3734797028554</v>
+        <v>113.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>42.46535284946236</v>
+        <v>38.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24942,10 +24942,10 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.543408614585474</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>13.30500861458557</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -25076,19 +25076,19 @@
         <v>230.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>104.2682114845818</v>
+        <v>281.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>350.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>345.078966540631</v>
       </c>
       <c r="Q34" t="n">
-        <v>435.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>436.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>72.37347970285543</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5.543408614585701</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>13.30500861458576</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25307,22 +25307,22 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>133.5476281577792</v>
+        <v>118.0018869658959</v>
       </c>
       <c r="M37" t="n">
-        <v>230.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>281.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>258.9224026384948</v>
+        <v>350.445564079015</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>435.839266425598</v>
       </c>
       <c r="R37" t="n">
         <v>436.6021279811511</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>5.543408614585758</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13.30500861458557</v>
       </c>
     </row>
     <row r="39">
@@ -25556,13 +25556,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>397.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>258.9224026384949</v>
       </c>
       <c r="R40" t="n">
-        <v>298.0766332913684</v>
+        <v>436.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>72.37347970285543</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>111.1565115808453</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25641,16 +25641,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>41.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>285.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>376.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>440.2212965486107</v>
+        <v>439.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25659,10 +25659,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>358.2867291657059</v>
       </c>
       <c r="Y41" t="n">
-        <v>302.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25687,7 +25687,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>115.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>26.53422560992942</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>223.3731429098285</v>
+        <v>106.0492222673723</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25751,22 +25751,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>78.11380033707866</v>
+        <v>77.11380033707866</v>
       </c>
       <c r="C43" t="n">
-        <v>63.72524664804467</v>
+        <v>62.72524664804467</v>
       </c>
       <c r="D43" t="n">
-        <v>76.53621805555548</v>
+        <v>75.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>71.98090483695654</v>
+        <v>70.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>65.38285596774193</v>
+        <v>64.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>36.04387284153003</v>
+        <v>35.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25778,31 +25778,31 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>79.52077380114304</v>
+        <v>78.52077380114304</v>
       </c>
       <c r="L43" t="n">
-        <v>214.5476281577792</v>
+        <v>213.5476281577792</v>
       </c>
       <c r="M43" t="n">
-        <v>311.6316114025499</v>
+        <v>310.6316114025499</v>
       </c>
       <c r="N43" t="n">
-        <v>362.1850752716849</v>
+        <v>361.1850752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>431.445564079015</v>
+        <v>430.445564079015</v>
       </c>
       <c r="P43" t="n">
-        <v>478.4478973282775</v>
+        <v>477.4478973282775</v>
       </c>
       <c r="Q43" t="n">
-        <v>516.839266425598</v>
+        <v>515.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>517.6021279811511</v>
+        <v>516.6021279811511</v>
       </c>
       <c r="S43" t="n">
-        <v>153.3734797028554</v>
+        <v>152.3734797028554</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>38.44364543010755</v>
+        <v>37.44364543010755</v>
       </c>
       <c r="Y43" t="n">
-        <v>78.46535284946236</v>
+        <v>77.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -25839,7 +25839,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>200.3951279027148</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -25881,22 +25881,22 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>331.8481678023229</v>
+        <v>334.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>423.6755817285639</v>
+        <v>426.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>486.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>469.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>478.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>429.2818334606677</v>
+        <v>214.4353577642217</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25924,13 +25924,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>165.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>172.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>57.12638589134853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,28 +25957,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>384.2737972923793</v>
+        <v>387.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>303.5639999646113</v>
+        <v>306.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>240.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>269.3731429098285</v>
+        <v>163.1265733159649</v>
       </c>
       <c r="X45" t="n">
-        <v>256.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>202.1425096737327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -25988,76 +25988,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>124.1138003370787</v>
+        <v>127.1138003370787</v>
       </c>
       <c r="C46" t="n">
-        <v>109.7252466480447</v>
+        <v>112.7252466480447</v>
       </c>
       <c r="D46" t="n">
-        <v>122.5362180555555</v>
+        <v>125.5362180555555</v>
       </c>
       <c r="E46" t="n">
-        <v>117.9809048369565</v>
+        <v>120.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>111.3828559677419</v>
+        <v>114.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>82.04387284153003</v>
+        <v>85.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>65.77112610161862</v>
+        <v>68.77112610161862</v>
       </c>
       <c r="I46" t="n">
-        <v>13.63345562011827</v>
+        <v>16.63345562011827</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>125.520773801143</v>
+        <v>128.520773801143</v>
       </c>
       <c r="L46" t="n">
-        <v>260.5476281577792</v>
+        <v>263.5476281577792</v>
       </c>
       <c r="M46" t="n">
-        <v>357.6316114025499</v>
+        <v>360.6316114025499</v>
       </c>
       <c r="N46" t="n">
-        <v>408.1850752716849</v>
+        <v>411.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>477.445564079015</v>
+        <v>480.445564079015</v>
       </c>
       <c r="P46" t="n">
-        <v>524.4478973282775</v>
+        <v>527.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>562.839266425598</v>
+        <v>565.839266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>563.6021279811511</v>
+        <v>566.6021279811511</v>
       </c>
       <c r="S46" t="n">
-        <v>199.3734797028554</v>
+        <v>202.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>47.02456650625771</v>
+        <v>50.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>36.17031021621619</v>
+        <v>39.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>63.37280983870968</v>
+        <v>66.37280983870968</v>
       </c>
       <c r="X46" t="n">
-        <v>84.44364543010755</v>
+        <v>87.44364543010755</v>
       </c>
       <c r="Y46" t="n">
-        <v>124.4653528494624</v>
+        <v>127.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7493722.763696278</v>
+        <v>7493085.104241411</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8269094.748512563</v>
+        <v>8272808.254535838</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9097453.327790113</v>
+        <v>9100970.431732254</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9924340.133002253</v>
+        <v>9927440.206176395</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10751226.9382144</v>
+        <v>10753909.98062054</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11471301.09082446</v>
+        <v>11475232.57840473</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12106064.40830342</v>
+        <v>12103916.90833469</v>
       </c>
     </row>
   </sheetData>
@@ -26290,28 +26290,28 @@
         <v>1310629.539202803</v>
       </c>
       <c r="I2" t="n">
-        <v>1310629.539202804</v>
+        <v>1310629.539202802</v>
       </c>
       <c r="J2" t="n">
-        <v>1196865.91732265</v>
+        <v>1196201.75721065</v>
       </c>
       <c r="K2" t="n">
-        <v>1234851.67952224</v>
+        <v>1241781.31343187</v>
       </c>
       <c r="L2" t="n">
-        <v>1316893.800893403</v>
+        <v>1316229.640781403</v>
       </c>
       <c r="M2" t="n">
-        <v>1316893.800893402</v>
+        <v>1316229.640781402</v>
       </c>
       <c r="N2" t="n">
-        <v>1316893.800893403</v>
+        <v>1316229.640781402</v>
       </c>
       <c r="O2" t="n">
-        <v>1149128.698038715</v>
+        <v>1151468.334187715</v>
       </c>
       <c r="P2" t="n">
-        <v>1010919.357466494</v>
+        <v>1001238.006925494</v>
       </c>
     </row>
     <row r="3">
@@ -26345,13 +26345,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>408896</v>
+        <v>408192</v>
       </c>
       <c r="K3" t="n">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="L3" t="n">
-        <v>58400</v>
+        <v>55200</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>72000</v>
+        <v>72800</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614572.6890979449</v>
+        <v>619423.6489515763</v>
       </c>
       <c r="C4" t="n">
-        <v>612819.846597504</v>
+        <v>617670.8064511353</v>
       </c>
       <c r="D4" t="n">
-        <v>611064.6262568065</v>
+        <v>615915.586110438</v>
       </c>
       <c r="E4" t="n">
-        <v>532233.5435599427</v>
+        <v>537035.2308443983</v>
       </c>
       <c r="F4" t="n">
-        <v>556508.1593539384</v>
+        <v>561309.8466383941</v>
       </c>
       <c r="G4" t="n">
-        <v>581143.3840644693</v>
+        <v>585945.0713489248</v>
       </c>
       <c r="H4" t="n">
-        <v>579471.0845346336</v>
+        <v>584272.7718190891</v>
       </c>
       <c r="I4" t="n">
-        <v>577796.4504475114</v>
+        <v>582598.1377319668</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524772.5813507028</v>
       </c>
       <c r="K4" t="n">
-        <v>538246.7750252959</v>
+        <v>546574.2240563536</v>
       </c>
       <c r="L4" t="n">
-        <v>580209.0187077393</v>
+        <v>584971.1143912999</v>
       </c>
       <c r="M4" t="n">
-        <v>578481.2401616639</v>
+        <v>583243.3358452244</v>
       </c>
       <c r="N4" t="n">
-        <v>576750.9773573431</v>
+        <v>581513.0730409037</v>
       </c>
       <c r="O4" t="n">
-        <v>488780.2918219594</v>
+        <v>494752.0968824982</v>
       </c>
       <c r="P4" t="n">
-        <v>417688.4362939645</v>
+        <v>417591.1960265165</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>73007.251</v>
       </c>
       <c r="J5" t="n">
-        <v>65913.92499999999</v>
+        <v>65792.325</v>
       </c>
       <c r="K5" t="n">
-        <v>67595.30499999999</v>
+        <v>67809.981</v>
       </c>
       <c r="L5" t="n">
-        <v>71378.41</v>
+        <v>71256.81</v>
       </c>
       <c r="M5" t="n">
-        <v>71378.41</v>
+        <v>71256.81</v>
       </c>
       <c r="N5" t="n">
-        <v>71378.41</v>
+        <v>71256.81</v>
       </c>
       <c r="O5" t="n">
-        <v>64568.821</v>
+        <v>64531.28999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>60701.647</v>
+        <v>60327.84</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>369198.0292595943</v>
+        <v>364347.0694059631</v>
       </c>
       <c r="C6" t="n">
-        <v>657830.8717600356</v>
+        <v>652979.9119064043</v>
       </c>
       <c r="D6" t="n">
-        <v>659586.0921007331</v>
+        <v>654735.1322471021</v>
       </c>
       <c r="E6" t="n">
-        <v>430112.2111147074</v>
+        <v>425310.5238302519</v>
       </c>
       <c r="F6" t="n">
-        <v>612217.2276836698</v>
+        <v>607415.5403992139</v>
       </c>
       <c r="G6" t="n">
-        <v>634078.9041383335</v>
+        <v>629277.2168538785</v>
       </c>
       <c r="H6" t="n">
-        <v>658151.2036681692</v>
+        <v>653349.5163837139</v>
       </c>
       <c r="I6" t="n">
-        <v>659825.8377552921</v>
+        <v>655024.1504708355</v>
       </c>
       <c r="J6" t="n">
-        <v>201732.9330383388</v>
+        <v>197444.8508599474</v>
       </c>
       <c r="K6" t="n">
-        <v>592209.5994969439</v>
+        <v>587397.1083755168</v>
       </c>
       <c r="L6" t="n">
-        <v>606906.3721856636</v>
+        <v>604801.7163901029</v>
       </c>
       <c r="M6" t="n">
-        <v>667034.1507317383</v>
+        <v>661729.4949361775</v>
       </c>
       <c r="N6" t="n">
-        <v>668764.4135360598</v>
+        <v>663459.7577404988</v>
       </c>
       <c r="O6" t="n">
-        <v>523779.5852167555</v>
+        <v>519384.9473052164</v>
       </c>
       <c r="P6" t="n">
-        <v>532529.2741725296</v>
+        <v>523318.9708989771</v>
       </c>
     </row>
   </sheetData>
@@ -26782,7 +26782,7 @@
         <v>225</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L2" t="n">
         <v>290</v>
@@ -26794,10 +26794,10 @@
         <v>290</v>
       </c>
       <c r="O2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P2" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -26883,25 +26883,25 @@
         <v>815</v>
       </c>
       <c r="J4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="K4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="M4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="N4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="O4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="P4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -26975,7 +26975,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -26999,19 +26999,19 @@
         <v>171</v>
       </c>
       <c r="K2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27231,7 +27231,7 @@
         <v>171</v>
       </c>
       <c r="P2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -27436,13 +27436,13 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,16 +27484,16 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>303.5095671255646</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>400</v>
+        <v>153.4284074428804</v>
       </c>
       <c r="W2" t="n">
         <v>400</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>57.41713069510382</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>341.6657683827116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>362.1445078762289</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27609,7 +27609,7 @@
         <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>250.6317583740469</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
@@ -27618,7 +27618,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27685,10 +27685,10 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>303.5095671255648</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27718,16 +27718,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>52.63096829726999</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>159.4007615079258</v>
       </c>
       <c r="S6" t="n">
-        <v>290.2120625142799</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27843,7 +27843,7 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>363.0586544920345</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
@@ -27894,10 +27894,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>325.6395755681846</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27922,7 +27922,7 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>52.63096829727004</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -27955,16 +27955,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>303.5095671255643</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27973,10 +27973,10 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>274.7686191606065</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28004,7 +28004,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28034,13 +28034,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>274.4424628029983</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,19 +28065,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>301.0505085398075</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28092,7 +28092,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>263.1227922624939</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28244,13 +28244,13 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>26.99048536749078</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28259,7 +28259,7 @@
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>19.11687125883935</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28490,16 +28490,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>166.1982915220775</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>166.1982915220774</v>
       </c>
       <c r="P15" t="n">
         <v>251</v>
@@ -28639,7 +28639,7 @@
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S17" t="n">
         <v>279</v>
@@ -28721,10 +28721,10 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28736,10 +28736,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>155.6705902671029</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>279</v>
@@ -28876,7 +28876,7 @@
         <v>279</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28906,7 +28906,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>275.5498086145856</v>
+        <v>279</v>
       </c>
       <c r="T20" t="n">
         <v>279</v>
@@ -28961,7 +28961,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -28973,10 +28973,10 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>155.6705902671029</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="P21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29110,7 +29110,7 @@
         <v>279</v>
       </c>
       <c r="H23" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29195,7 +29195,7 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -29210,10 +29210,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
-      </c>
-      <c r="P24" t="n">
-        <v>155.670590267103</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29566,25 +29566,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I29" t="n">
         <v>150.0811596826846</v>
@@ -29614,28 +29614,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="S29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="T29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="U29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="V29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="W29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="X29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Y29" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30">
@@ -29645,76 +29645,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I30" t="n">
-        <v>245</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>245</v>
+        <v>238.6810271489408</v>
       </c>
       <c r="M30" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="P30" t="n">
-        <v>43.02565607671421</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="R30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="S30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="T30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="U30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="V30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="W30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="X30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Y30" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31">
@@ -29724,76 +29724,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="O31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="P31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="R31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="S31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="T31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="U31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="V31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="W31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="X31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Y31" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32">
@@ -29903,7 +29903,7 @@
         <v>290</v>
       </c>
       <c r="I33" t="n">
-        <v>244.3204219169347</v>
+        <v>290</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29924,7 +29924,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>290</v>
+        <v>244.3204219169346</v>
       </c>
       <c r="Q33" t="n">
         <v>290</v>
@@ -30149,10 +30149,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>244.3204219169348</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>244.3204219169345</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -30380,28 +30380,28 @@
         <v>290</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>244.3204219169346</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>290</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>71.24115682645521</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>290</v>
@@ -30514,25 +30514,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30562,28 +30562,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42">
@@ -30593,76 +30593,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J42" t="n">
-        <v>137.1733415776632</v>
+        <v>210</v>
       </c>
       <c r="K42" t="n">
-        <v>209</v>
+        <v>142.5380088334107</v>
       </c>
       <c r="L42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43">
@@ -30672,76 +30672,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I43" t="n">
-        <v>209</v>
+        <v>201.6863313363712</v>
       </c>
       <c r="J43" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U43" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
-        <v>205.7472434881925</v>
+        <v>210</v>
       </c>
       <c r="W43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="U44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="V44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="W44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="X44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Y44" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45">
@@ -30830,76 +30830,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J45" t="n">
-        <v>163</v>
+        <v>12.83215864645137</v>
       </c>
       <c r="K45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O45" t="n">
-        <v>20.33215864645137</v>
+        <v>160</v>
       </c>
       <c r="P45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="R45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="U45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="V45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="W45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="X45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Y45" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J46" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="R46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="U46" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="W46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="X46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Y46" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -34749,7 +34749,7 @@
         <v>815</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003026867</v>
+        <v>783.0093003026417</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.03070753915023</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>21.8606322724283</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
@@ -34904,7 +34904,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,7 +34931,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34983,10 +34983,10 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
-        <v>783.0093003025956</v>
+        <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>815</v>
+        <v>783.0093003025988</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
@@ -35129,7 +35129,7 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>118.0147816505045</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35180,10 +35180,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>38.17422271872228</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,10 +35220,10 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003026599</v>
+        <v>815</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>783.0093003026119</v>
       </c>
       <c r="M8" t="n">
         <v>815</v>
@@ -35351,19 +35351,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>13.93670820272891</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35378,7 +35378,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>112.164400988036</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>814.9999999999999</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>116.7428182785516</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>218.0943400082821</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35545,7 +35545,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>153.7434213674942</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35697,16 +35697,16 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>237.4900058455003</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35776,16 +35776,16 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>300.8248416307323</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>407.6553134248237</v>
       </c>
       <c r="P15" t="n">
         <v>364.6660045146532</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>116.7428182785515</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>815</v>
+        <v>815.0000000000002</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>66.38559440267282</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,10 +36007,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>280.8791965047787</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36022,10 +36022,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>397.1276121698493</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>105.9207349095204</v>
@@ -36171,7 +36171,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>536.4810879374849</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>164.5104768795733</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,10 +36259,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>397.1276121698493</v>
+        <v>397.1276121698494</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>116.7428182785515</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
         <v>815</v>
@@ -36417,13 +36417,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>164.5104768795733</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>125.2086062376757</v>
+        <v>280.8791965047787</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
@@ -36496,10 +36496,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>269.3365947817561</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>354.8631703024886</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>773.0000000000003</v>
+        <v>771.0000000000034</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>34.28825465734733</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>773</v>
+        <v>757.5205960563293</v>
       </c>
       <c r="M29" t="n">
-        <v>113.18697554247</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
@@ -36952,31 +36952,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>27.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>370.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>436.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>519.0913753486871</v>
+        <v>512.7724024976278</v>
       </c>
       <c r="M30" t="n">
-        <v>331.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N30" t="n">
-        <v>134.6265501086548</v>
+        <v>383.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>241.4570219027464</v>
+        <v>490.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>156.6916605913674</v>
+        <v>362.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>71.92073490952041</v>
+        <v>75.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37025,16 +37025,16 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3.956127158469968</v>
       </c>
       <c r="H31" t="n">
-        <v>16.22887389838138</v>
+        <v>20.22887389838138</v>
       </c>
       <c r="I31" t="n">
-        <v>68.36654437988173</v>
+        <v>72.36654437988173</v>
       </c>
       <c r="J31" t="n">
-        <v>209.7310511640922</v>
+        <v>213.7310511640922</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -37064,19 +37064,19 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>34.97543349374229</v>
+        <v>38.97543349374229</v>
       </c>
       <c r="U31" t="n">
-        <v>94.04160872554206</v>
+        <v>98.04160872554206</v>
       </c>
       <c r="V31" t="n">
-        <v>45.82968978378381</v>
+        <v>49.82968978378381</v>
       </c>
       <c r="W31" t="n">
-        <v>18.62719016129032</v>
+        <v>22.62719016129032</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.556354569892449</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773</v>
+        <v>771.000000000013</v>
       </c>
       <c r="K32" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L32" t="n">
-        <v>304.7028254483104</v>
+        <v>771</v>
       </c>
       <c r="M32" t="n">
-        <v>773</v>
+        <v>771.000000000013</v>
       </c>
       <c r="N32" t="n">
-        <v>773</v>
+        <v>771.000000000013</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000016</v>
+        <v>771.000000000013</v>
       </c>
       <c r="P32" t="n">
-        <v>772.7129399593185</v>
+        <v>771.000000000013</v>
       </c>
       <c r="Q32" t="n">
-        <v>773</v>
+        <v>708.4459161612166</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>27.19403602558618</v>
+        <v>72.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>403.6660045146532</v>
+        <v>357.9864264315877</v>
       </c>
       <c r="Q33" t="n">
         <v>116.9207349095204</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>360.540647884545</v>
+        <v>762.8578586788261</v>
       </c>
       <c r="M35" t="n">
-        <v>773</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="N35" t="n">
-        <v>773</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="O35" t="n">
-        <v>773</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="P35" t="n">
-        <v>773.000000000001</v>
+        <v>770.7129399593388</v>
       </c>
       <c r="Q35" t="n">
-        <v>773</v>
+        <v>771.0000000000202</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,10 +37435,10 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>518.4117972656217</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>86.95004216450428</v>
+        <v>331.2704640814388</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="K38" t="n">
-        <v>773</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L38" t="n">
-        <v>304.4157654076137</v>
+        <v>762.5707986380528</v>
       </c>
       <c r="M38" t="n">
-        <v>773</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="N38" t="n">
-        <v>773</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000016</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="P38" t="n">
-        <v>773</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="Q38" t="n">
-        <v>773</v>
+        <v>771.0000000000275</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>72.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>415.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37678,16 +37678,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>205.86770693511</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>241.4570219027464</v>
+        <v>485.777443819681</v>
       </c>
       <c r="P39" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>116.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>611.8542523944722</v>
+        <v>210.6733301342152</v>
       </c>
       <c r="O41" t="n">
-        <v>773.0000000000016</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37903,28 +37903,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>262.3819478153389</v>
+        <v>335.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>400.1038546407913</v>
+        <v>333.6418634742021</v>
       </c>
       <c r="L42" t="n">
-        <v>483.091375348687</v>
+        <v>484.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>295.9500421645043</v>
+        <v>296.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>343.6265501086548</v>
+        <v>344.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>450.4570219027464</v>
+        <v>451.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>322.6660045146532</v>
+        <v>323.6660045146532</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.92073490952041</v>
+        <v>36.92073490952041</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,7 +37979,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>32.36654437988173</v>
+        <v>25.05287571625292</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -38018,7 +38018,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>6.576933271976253</v>
+        <v>10.82968978378381</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>770.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,13 +38076,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>429.5499849984178</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>288.2086062376757</v>
+        <v>138.0407648841271</v>
       </c>
       <c r="K45" t="n">
-        <v>354.1038546407913</v>
+        <v>351.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>437.091375348687</v>
+        <v>434.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>249.9500421645043</v>
+        <v>246.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>297.6265501086548</v>
+        <v>294.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>261.7891805491977</v>
+        <v>401.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>276.6660045146532</v>
+        <v>273.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
